--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f6901b12a822f6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ec255f7dfd4501</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f6901b12a822f6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Infrastructure &amp; Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ec255f7dfd4501</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II, AWS Data Platform</t>
+          <t>Data Engineer (USI8)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Augusta, KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
+          <t>https://www.indeed.com/viewjob?jk=9074f3b618d5628b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer (USI8)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=b63514d290d45e42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Data Engineer (USI8)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5214f9a2298f5d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer (USI8)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,137 +1021,137 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=73dd95c802d8f62b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Sr Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Data Engineer II, AWS Data Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
+          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,54 +1476,54 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer II - AI/ML Engineering</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Engineer II - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Verana Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe Experience Platform)</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b472336df73668</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,19 +2176,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – POS</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - DataOps</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Data Engineer - DataOps</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MedeAnalytics</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Dimensional Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffa1810d5da5d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Data Science &amp; Machine Learning Intern</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>RockWallet</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,102 +3121,102 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Scientist - Data Platforms - I&amp;D</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,157 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Scientist - Data Platforms - I&amp;D</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Jabil</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,52 +1098,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II, AWS Data Platform</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Engineer II - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer II - AI/ML Engineering</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
+          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Data Engineer - DataOps</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
+          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - DataOps</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
+          <t>Data Science &amp; Machine Learning Intern</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>RockWallet</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Scientist - Data Platforms - I&amp;D</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,15 +3776,225 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CaseGuard</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Jabil</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
         </is>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (USI8)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Augusta, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f6901b12a822f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9074f3b618d5628b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (USI8)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ec255f7dfd4501</t>
+          <t>https://www.indeed.com/viewjob?jk=b63514d290d45e42</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Augusta, KS, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9074f3b618d5628b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5214f9a2298f5d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63514d290d45e42</t>
+          <t>https://www.indeed.com/viewjob?jk=73dd95c802d8f62b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer (USI8)</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5214f9a2298f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (USI8)</t>
+          <t>Sr Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dd95c802d8f62b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Infrastructure &amp; Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,64 +1116,64 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Engineer II - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer II - AI/ML Engineering</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
+          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - DataOps</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Data Science &amp; Machine Learning Intern</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RockWallet</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,120 +3881,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Jabil</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior DevOps Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
         </is>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>IT Site Reliability Engineer — API Management Platforms</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer II - AI/ML Engineering</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Engineer II - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Data Science &amp; Machine Learning Intern</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>RockWallet</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,50 +3846,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior DevOps Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
         </is>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
@@ -2008,25 +2008,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Science &amp; Machine Learning Intern</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>RockWallet</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,87 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>REI Systems</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Science &amp; Machine Learning Intern</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>RockWallet</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3855,76 +3855,6 @@
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior DevOps Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>REI Systems</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer (USI8)</t>
+          <t>Sr Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Augusta, KS, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9074f3b618d5628b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer (USI8)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63514d290d45e42</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer (USI8)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,137 +916,137 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5214f9a2298f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer (USI8)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dd95c802d8f62b</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Infrastructure &amp; Security Engineer</t>
+          <t>IT Site Reliability Engineer — API Management Platforms</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
+          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,137 +1056,137 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer — API Management Platforms</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Engineer II - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II - AI/ML Engineering</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Data Science &amp; Machine Learning Intern</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>RockWallet</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3750,111 +3750,6 @@
         </is>
       </c>
       <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior DevOps Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>REI Systems</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Sr Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Infrastructure &amp; Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>IT Site Reliability Engineer — API Management Platforms</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer — API Management Platforms</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Engineer II - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer II - AI/ML Engineering</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Azure Platform Senior Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Data Science &amp; Machine Learning Intern</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>RockWallet</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,29 +3146,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>DemandTec</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3680,76 +3680,6 @@
         </is>
       </c>
       <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior DevOps Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>REI Systems</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,12 +573,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
+          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,84 +601,84 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b6ef3996106ead</t>
+          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
+          <t>Senior Backend Software Engineer / Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>NYC IT Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Kareem Networks LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
+          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Infrastructure &amp; Security Engineer</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer — API Management Platforms</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>IT Site Reliability Engineer — API Management Platforms</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Curriculum Associates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba3cd5dfb638d55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Pega PRPC Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer II - AI/ML Engineering</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
+          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Engineer II - AI/ML Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Platform Senior Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Azure Platform Senior Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Infrastructure, AI Labs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mariner Wealth Advisors</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Data Science &amp; Machine Learning Intern</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>RockWallet</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,29 +3146,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DemandTec</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>DemandTec</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
+          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,15 +3671,85 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Agents</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>TetraScience</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>REI Systems</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d27925e100760a</t>
+          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Senior Backend Software Engineer / Consultant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NYC IT Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363583288a17b581</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kareem Networks LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ed17078e339db4</t>
+          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,137 +601,137 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
+          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer / Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NYC IT Inc</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kareem Networks LLC</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
@@ -753,125 +753,125 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Infrastructure &amp; Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VizyPay</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waukee, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Site Reliability Engineer — API Management Platforms</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,172 +916,172 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Curriculum Associates</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba3cd5dfb638d55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer — API Management Platforms</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Curriculum Associates</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba3cd5dfb638d55</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pega PRPC Administrator</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeae0705aa36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b861154fd37cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer II - AI/ML Engineering</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, PySpark, Scala, Kafka, MLOps</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe877c82bf3765bf</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Azure Platform Senior Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Software Engineer, Infrastructure, AI Labs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,129 +1896,129 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Enterprise IT Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Hoffman Estates, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Azure Platform Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure, AI Labs</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer, Threat Intelligence Services</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, PostgreSQL, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c8b9c11f3d882f</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Science &amp; Machine Learning Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RockWallet</t>
+          <t>DemandTec</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, PySpark, Power BI, Tableau, Git</t>
+          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce12f322d42133b</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1837fbface65052</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3400,356 +3400,6 @@
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>DemandTec</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Associate - Quality Engineer, AI &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf417995b86a8947</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Jabil</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior DevOps Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Agents</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>TetraScience</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>REI Systems</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
+          <t>Senior Backend Software Engineer / Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>NYC IT Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer / Consultant</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NYC IT Inc</t>
+          <t>Kareem Networks LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,49 +531,49 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kareem Networks LLC</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
+          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,52 +766,52 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Senior Enterprise IT Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hoffman Estates, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Enterprise IT Architect</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hoffman Estates, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DemandTec</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DemandTec</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>
       </c>
     </row>
@@ -3367,41 +3367,6 @@
       <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e1837fbface65052</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>REI Systems</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Sr. Salesforce Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c5cc701830f318</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,42 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,77 +1291,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,94 +1371,94 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, BigQuery, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure Platform Senior Engineer</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,94 +1826,94 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure, AI Labs</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Azure Platform Senior Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Enterprise IT Architect</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hoffman Estates, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Software Engineer, Infrastructure, AI Labs</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Enterprise IT Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Hoffman Estates, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,112 +2026,112 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DemandTec</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DemandTec</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,87 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e1837fbface65052</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>REI Systems</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer / Consultant</t>
+          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NYC IT Inc</t>
+          <t>Arity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
+          <t>AWS, Redshift, Athena, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Backend Software Engineer / Consultant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kareem Networks LLC</t>
+          <t>NYC IT Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,49 +531,49 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Kareem Networks LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
+          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
+          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer — API Management Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Platform Engineer</t>
+          <t>IT Site Reliability Engineer — API Management Platforms</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c5cc701830f318</t>
+          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Sr. Salesforce Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c5cc701830f318</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Curriculum Associates</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba3cd5dfb638d55</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Curriculum Associates</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba3cd5dfb638d55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, BigQuery, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, BigQuery, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure, AI Labs</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Enterprise IT Architect</t>
+          <t>Software Engineer, Infrastructure, AI Labs</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hoffman Estates, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Senior Enterprise IT Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Hoffman Estates, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DemandTec</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,29 +3041,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>DemandTec</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1837fbface65052</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,87 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>REI Systems</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1837fbface65052</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Reveal Global Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fulton, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
+          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,129 +671,129 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>AI/Data Science Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer — API Management Platforms</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Platform Engineer</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,172 +951,172 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c5cc701830f318</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Curriculum Associates</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba3cd5dfb638d55</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>IT Site Reliability Engineer — API Management Platforms</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Sr. Salesforce Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c5cc701830f318</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,112 +1221,112 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, BigQuery, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,137 +1476,137 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, BigQuery, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,207 +1791,207 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>GK POS: GKPOS Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Platform Senior Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure, AI Labs</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2022,46 +2022,46 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Enterprise IT Architect</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hoffman Estates, IL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Azure Platform Senior Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed3b3fbe175a19b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer, Infrastructure, AI Labs</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,137 +2491,137 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Enterprise IT Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hoffman Estates, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,102 +2911,102 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DemandTec</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,567 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1837fbface65052</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Protera Health</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Medallia</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Sargent &amp; Lundy</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DemandTec</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Rosslyn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior DevOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Agents</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TetraScience</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>REI Systems</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>DevOps Engineer - Plano, TX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Senior Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,42 +1406,42 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, BigQuery, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, BigQuery, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>GK POS: GKPOS Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GK POS: GKPOS Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7770b8e6473c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wayne, NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Azure Platform Senior Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Azure Platform Senior Engineer</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed3b3fbe175a19b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed3b3fbe175a19b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure, AI Labs</t>
+          <t>Senior Enterprise IT Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hoffman Estates, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Enterprise IT Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hoffman Estates, IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,104 +2586,104 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Oracle ERP Data Expert</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
+          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,59 +3261,59 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Infrastructure &amp; Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>DemandTec</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DemandTec</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,85 +3986,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Agents</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>TetraScience</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>REI Systems</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
         </is>

--- a/results/job_matches_2026-08-13.xlsx
+++ b/results/job_matches_2026-08-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arity</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>39.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Azure</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
+          <t>https://www.indeed.com/viewjob?jk=22e1c75da6c86a08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer / Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NYC IT Inc</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>39.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b609663c97ff4ea</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kareem Networks LLC</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>39.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
+          <t>https://www.indeed.com/viewjob?jk=debc4a58840e5d41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reveal Global Consulting</t>
+          <t>Arity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fulton, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, Redshift, Athena, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Senior Backend Software Engineer / Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NYC IT Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Kareem Networks LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
+          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Reveal Global Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fulton, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
+          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
+          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=673be08859dddab2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI/Data Science Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4bf5dedcf41447</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Springs Window Fashions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
+          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>AI/Data Science Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=79151862d72c4127</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer — API Management Platforms</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Platform Engineer</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c5cc701830f318</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Software Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cranial Technologies</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Site Reliability Engineer — API Management Platforms</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,94 +1231,94 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
+          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Salesforce Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c5cc701830f318</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Site Reliability Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Cranial Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, EMR, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb450ac5eb4304ae</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Plano, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf529eb38d0229</t>
+          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Architect - Contract - Remote</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Oracle PL/SQL Developer</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadcf53dc0861d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,42 +1441,42 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Data Architect - Contract - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9924556265e3c9</t>
         </is>
       </c>
     </row>
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, BigQuery, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,89 +1686,89 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Associate - Technology Operations Engineering</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, BigQuery, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=f724dd5d2a21f911</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GK POS: GKPOS Developer</t>
+          <t>Senior Associate - Technology Operations Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcbeb3d55a273f2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GK POS: GKPOS Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
         </is>
       </c>
     </row>
@@ -1903,60 +1903,60 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wayne, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Senior Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Azure Platform Senior Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed3b3fbe175a19b</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed3b3fbe175a19b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Platform Senior Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd9cef29d42fb9a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Tech Anchor - Supply Chain</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Enterprise IT Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hoffman Estates, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=077f2ff2bedb0647</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Enterprise IT Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Hoffman Estates, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>RDS, Azure, Blob Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7aafa933dd9ce1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Oracle ERP Data Expert</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fanisko</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be507a87bcb355e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Sr Software Engineer (Site Reliability) Austin or Dallas, TX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, Scala, PostgreSQL, Data Modeling, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=78e458c132c387b3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,59 +3261,59 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Full Stack Engineer - AI Forward</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=a64052bb51ee98f7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>QA Test Engineer - Digital Products</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Penske Truck Leasing</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer 5</t>
+          <t>QA Test Engineer - Digital Products</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Penske Truck Leasing</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d0dc537de6d884</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Software Development Engineer 5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, MySQL, MongoDB, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=98f20089a25d422a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, GovCloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eae24a52542621</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Senior Site Reliability Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5f12797f9848e1</t>
         </is>
       </c>
     </row>
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4b1a61008e4755</t>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DemandTec</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,29 +3916,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316dfc218c18008e</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>DemandTec</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,217 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277aa9aed0774afa</t>
+          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Rosslyn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
         </is>
       </c>
     </row>
